--- a/data/gravel/Ghost Asket CF 2025.xlsx
+++ b/data/gravel/Ghost Asket CF 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C409410-C331-BA4F-9BC5-A1E5CB293D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94533EFD-32A5-C44A-8768-1B2BC57A626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2100" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,9 +329,6 @@
     <t>gravel</t>
   </si>
   <si>
-    <t>https://www.ghost-bikes.com/gb-en/bikes/gravel/</t>
-  </si>
-  <si>
     <t>Waldsassen, Bavaria, Germany</t>
   </si>
   <si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>a8:g31</t>
+  </si>
+  <si>
+    <t>https://www.ghost-bikes.com/de-en/bikes/gravel/</t>
   </si>
 </sst>
 </file>
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -759,12 +759,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -783,7 +783,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>67</v>
@@ -1252,7 +1252,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1260,7 +1260,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1409,7 +1409,7 @@
         <v>52</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1417,7 +1417,7 @@
         <v>53</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>60</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1477,7 +1477,7 @@
         <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1485,7 +1485,7 @@
         <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1512,7 +1512,7 @@
         <v>66</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1520,7 +1520,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
